--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/96.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/96.xlsx
@@ -426,13 +426,13 @@
         <v>-11.15778511464839</v>
       </c>
       <c r="E2">
-        <v>-12.88364195427599</v>
+        <v>-13.35319942413133</v>
       </c>
       <c r="F2">
-        <v>-3.249197560029719</v>
+        <v>-3.783338801763674</v>
       </c>
       <c r="G2">
-        <v>-9.957883773517237</v>
+        <v>-8.6966321339657</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.46800242961696</v>
       </c>
       <c r="E3">
-        <v>-13.77669325638065</v>
+        <v>-13.87572192598038</v>
       </c>
       <c r="F3">
-        <v>-3.360608005501836</v>
+        <v>-3.837058427835222</v>
       </c>
       <c r="G3">
-        <v>-8.879831103017889</v>
+        <v>-8.729585304263606</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.690928101920166</v>
       </c>
       <c r="E4">
-        <v>-15.46189240275105</v>
+        <v>-14.06915116474401</v>
       </c>
       <c r="F4">
-        <v>-3.03356524140698</v>
+        <v>-4.005091098758296</v>
       </c>
       <c r="G4">
-        <v>-9.511688445734267</v>
+        <v>-8.433602669779527</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.910632795616554</v>
       </c>
       <c r="E5">
-        <v>-15.03835328576166</v>
+        <v>-15.45739109958742</v>
       </c>
       <c r="F5">
-        <v>-3.321119731410384</v>
+        <v>-3.813027489480008</v>
       </c>
       <c r="G5">
-        <v>-8.702759953758891</v>
+        <v>-8.392095049808143</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.121874355497608</v>
       </c>
       <c r="E6">
-        <v>-14.96065372873805</v>
+        <v>-16.04712974113233</v>
       </c>
       <c r="F6">
-        <v>-3.190969958552137</v>
+        <v>-3.764591190703516</v>
       </c>
       <c r="G6">
-        <v>-8.769523725649373</v>
+        <v>-7.852770765459935</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.33703034071215</v>
       </c>
       <c r="E7">
-        <v>-15.96188574641194</v>
+        <v>-17.1233261175292</v>
       </c>
       <c r="F7">
-        <v>-3.617843420195375</v>
+        <v>-3.96015713736084</v>
       </c>
       <c r="G7">
-        <v>-8.37058312489396</v>
+        <v>-7.289209977218722</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.565852561436487</v>
       </c>
       <c r="E8">
-        <v>-17.63004877356548</v>
+        <v>-17.01493709215561</v>
       </c>
       <c r="F8">
-        <v>-3.524763916979809</v>
+        <v>-3.852445352342223</v>
       </c>
       <c r="G8">
-        <v>-7.633089584564978</v>
+        <v>-7.329893271350826</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.81722072470438</v>
       </c>
       <c r="E9">
-        <v>-16.98902063540971</v>
+        <v>-18.23308754327092</v>
       </c>
       <c r="F9">
-        <v>-3.566363699580997</v>
+        <v>-4.035218821198114</v>
       </c>
       <c r="G9">
-        <v>-8.361720794485331</v>
+        <v>-7.195925425013139</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.087014181981737</v>
       </c>
       <c r="E10">
-        <v>-17.66023105282661</v>
+        <v>-18.48214455674477</v>
       </c>
       <c r="F10">
-        <v>-3.434085022497555</v>
+        <v>-4.035468159786357</v>
       </c>
       <c r="G10">
-        <v>-7.615712531029343</v>
+        <v>-6.1606218290624</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.392594596542685</v>
       </c>
       <c r="E11">
-        <v>-19.68545519853695</v>
+        <v>-19.44677291901466</v>
       </c>
       <c r="F11">
-        <v>-3.615702090459138</v>
+        <v>-3.961563705210793</v>
       </c>
       <c r="G11">
-        <v>-7.637055618121025</v>
+        <v>-6.640154350425831</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.73875464572483</v>
       </c>
       <c r="E12">
-        <v>-19.18358253816287</v>
+        <v>-20.53387838929601</v>
       </c>
       <c r="F12">
-        <v>-3.691078553909477</v>
+        <v>-4.150786842664882</v>
       </c>
       <c r="G12">
-        <v>-6.475941360041363</v>
+        <v>-6.158728197013937</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.128007146916336</v>
       </c>
       <c r="E13">
-        <v>-20.10525832447001</v>
+        <v>-20.66967373936402</v>
       </c>
       <c r="F13">
-        <v>-3.424304488572701</v>
+        <v>-3.949783492375582</v>
       </c>
       <c r="G13">
-        <v>-5.612547772853898</v>
+        <v>-5.485068595773182</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.578025721298693</v>
       </c>
       <c r="E14">
-        <v>-19.69864211484728</v>
+        <v>-21.60015740761608</v>
       </c>
       <c r="F14">
-        <v>-3.48838367738366</v>
+        <v>-3.524004304071441</v>
       </c>
       <c r="G14">
-        <v>-5.253035769471204</v>
+        <v>-4.917472252519598</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.094717871571378</v>
       </c>
       <c r="E15">
-        <v>-23.27404442591532</v>
+        <v>-21.86097486808785</v>
       </c>
       <c r="F15">
-        <v>-3.214191581954815</v>
+        <v>-3.456425262983655</v>
       </c>
       <c r="G15">
-        <v>-5.439647910974382</v>
+        <v>-4.55362012393492</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.679594590898368</v>
       </c>
       <c r="E16">
-        <v>-22.18560305580171</v>
+        <v>-23.17316361044645</v>
       </c>
       <c r="F16">
-        <v>-2.680853028234173</v>
+        <v>-3.40469786051584</v>
       </c>
       <c r="G16">
-        <v>-5.052039307599894</v>
+        <v>-4.244441654931305</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.342166875123228</v>
       </c>
       <c r="E17">
-        <v>-22.93901433340584</v>
+        <v>-23.61428679200763</v>
       </c>
       <c r="F17">
-        <v>-2.904605004139153</v>
+        <v>-3.44512633160947</v>
       </c>
       <c r="G17">
-        <v>-4.317730512079691</v>
+        <v>-4.042160701390757</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.078711380762545</v>
       </c>
       <c r="E18">
-        <v>-22.72413371326788</v>
+        <v>-24.7406088471954</v>
       </c>
       <c r="F18">
-        <v>-2.722199330410105</v>
+        <v>-2.801834430678235</v>
       </c>
       <c r="G18">
-        <v>-4.99273088426385</v>
+        <v>-3.794038623767921</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.8792539202518426</v>
       </c>
       <c r="E19">
-        <v>-25.10219391128585</v>
+        <v>-25.37103129922521</v>
       </c>
       <c r="F19">
-        <v>-2.044988269436439</v>
+        <v>-2.828030721424367</v>
       </c>
       <c r="G19">
-        <v>-4.498499540706055</v>
+        <v>-4.063199218292826</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.7379722276021604</v>
       </c>
       <c r="E20">
-        <v>-26.3619882093757</v>
+        <v>-25.84790225460294</v>
       </c>
       <c r="F20">
-        <v>-2.14388953875888</v>
+        <v>-2.461244546077996</v>
       </c>
       <c r="G20">
-        <v>-3.714469661731538</v>
+        <v>-3.330016008255975</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6405269176318509</v>
       </c>
       <c r="E21">
-        <v>-26.95732404479408</v>
+        <v>-26.54699901495907</v>
       </c>
       <c r="F21">
-        <v>-1.783368306079882</v>
+        <v>-2.294295379717784</v>
       </c>
       <c r="G21">
-        <v>-3.929393588686562</v>
+        <v>-2.894887834210788</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5723497900324526</v>
       </c>
       <c r="E22">
-        <v>-26.74610243165431</v>
+        <v>-27.25310132460507</v>
       </c>
       <c r="F22">
-        <v>-1.730931821115271</v>
+        <v>-1.825255532169842</v>
       </c>
       <c r="G22">
-        <v>-3.720117452421535</v>
+        <v>-3.536054430983596</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.5257781552635048</v>
       </c>
       <c r="E23">
-        <v>-27.67704800425516</v>
+        <v>-26.87935277933001</v>
       </c>
       <c r="F23">
-        <v>-1.508396716925003</v>
+        <v>-1.388037418400443</v>
       </c>
       <c r="G23">
-        <v>-3.267873757938315</v>
+        <v>-2.658150722697505</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.4925381474641194</v>
       </c>
       <c r="E24">
-        <v>-27.44671170232901</v>
+        <v>-28.60380926687291</v>
       </c>
       <c r="F24">
-        <v>-1.493877921456136</v>
+        <v>-1.333244228174867</v>
       </c>
       <c r="G24">
-        <v>-3.18926816465386</v>
+        <v>-3.443286323882139</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.4677109516516</v>
       </c>
       <c r="E25">
-        <v>-28.14586280437324</v>
+        <v>-28.13443293597788</v>
       </c>
       <c r="F25">
-        <v>-1.22773093024328</v>
+        <v>-1.165596748094095</v>
       </c>
       <c r="G25">
-        <v>-3.863245578266385</v>
+        <v>-3.077077086873499</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.4514621169913096</v>
       </c>
       <c r="E26">
-        <v>-28.47735163020871</v>
+        <v>-28.4529023990413</v>
       </c>
       <c r="F26">
-        <v>-1.07935293268643</v>
+        <v>-1.123589408730729</v>
       </c>
       <c r="G26">
-        <v>-2.845544152947951</v>
+        <v>-3.077421383609583</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.4433812731836356</v>
       </c>
       <c r="E27">
-        <v>-28.33143061225955</v>
+        <v>-28.20298497550599</v>
       </c>
       <c r="F27">
-        <v>-0.5538043460217145</v>
+        <v>-0.6245568626296258</v>
       </c>
       <c r="G27">
-        <v>-3.86985342716277</v>
+        <v>-3.860891780387963</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4434692317802787</v>
       </c>
       <c r="E28">
-        <v>-27.99323511641871</v>
+        <v>-28.26108076855039</v>
       </c>
       <c r="F28">
-        <v>-1.023693270157526</v>
+        <v>-1.240499385390032</v>
       </c>
       <c r="G28">
-        <v>-4.156851241053268</v>
+        <v>-3.641432406044137</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.4519415894247906</v>
       </c>
       <c r="E29">
-        <v>-29.58472202167438</v>
+        <v>-28.12893084005856</v>
       </c>
       <c r="F29">
-        <v>-1.008804194459607</v>
+        <v>-1.166097910372789</v>
       </c>
       <c r="G29">
-        <v>-3.813441731173589</v>
+        <v>-3.709450874694002</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.4661751319712784</v>
       </c>
       <c r="E30">
-        <v>-28.02656921358918</v>
+        <v>-27.75013304626495</v>
       </c>
       <c r="F30">
-        <v>-0.5549582618138141</v>
+        <v>-1.016744096015441</v>
       </c>
       <c r="G30">
-        <v>-4.963157780961541</v>
+        <v>-4.292669682347408</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.4815782551670186</v>
       </c>
       <c r="E31">
-        <v>-27.92786659411799</v>
+        <v>-27.54629737423169</v>
       </c>
       <c r="F31">
-        <v>-0.61018634492586</v>
+        <v>-1.003764407180975</v>
       </c>
       <c r="G31">
-        <v>-4.481973297374013</v>
+        <v>-4.999649924440927</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.4934947625203974</v>
       </c>
       <c r="E32">
-        <v>-27.39782682541621</v>
+        <v>-28.52801619740653</v>
       </c>
       <c r="F32">
-        <v>-0.8595315601077336</v>
+        <v>-0.7639379618246707</v>
       </c>
       <c r="G32">
-        <v>-3.961979288429609</v>
+        <v>-4.35979430370167</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.4959112613669971</v>
       </c>
       <c r="E33">
-        <v>-27.20864529527177</v>
+        <v>-26.50979307251205</v>
       </c>
       <c r="F33">
-        <v>-1.07187857361097</v>
+        <v>-1.045261472224216</v>
       </c>
       <c r="G33">
-        <v>-4.031523918573079</v>
+        <v>-4.664688926777468</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.4834984060007905</v>
       </c>
       <c r="E34">
-        <v>-27.80408528559233</v>
+        <v>-27.14961210810778</v>
       </c>
       <c r="F34">
-        <v>-1.388665320891765</v>
+        <v>-0.8483237491478562</v>
       </c>
       <c r="G34">
-        <v>-4.463593148539979</v>
+        <v>-4.921355522437163</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4523972050340133</v>
       </c>
       <c r="E35">
-        <v>-26.7208833599056</v>
+        <v>-26.62334908672839</v>
       </c>
       <c r="F35">
-        <v>-1.084978375718841</v>
+        <v>-1.190523151611735</v>
       </c>
       <c r="G35">
-        <v>-4.660487844488133</v>
+        <v>-3.66408646916937</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.3984915984354035</v>
       </c>
       <c r="E36">
-        <v>-27.32371834828068</v>
+        <v>-26.57412910273903</v>
       </c>
       <c r="F36">
-        <v>-1.173539134752137</v>
+        <v>-1.075159736893459</v>
       </c>
       <c r="G36">
-        <v>-3.953544018395546</v>
+        <v>-4.861821982004449</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3206187891205718</v>
       </c>
       <c r="E37">
-        <v>-25.44074715657329</v>
+        <v>-25.5949598104305</v>
       </c>
       <c r="F37">
-        <v>-1.140522895178757</v>
+        <v>-1.176811185993195</v>
       </c>
       <c r="G37">
-        <v>-4.263467360145497</v>
+        <v>-4.865711873013093</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.219937422262668</v>
       </c>
       <c r="E38">
-        <v>-24.08532054438946</v>
+        <v>-25.44206494250952</v>
       </c>
       <c r="F38">
-        <v>-1.03768770906042</v>
+        <v>-1.035262249305023</v>
       </c>
       <c r="G38">
-        <v>-5.58532846743001</v>
+        <v>-4.028471595585871</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.09871621388869049</v>
       </c>
       <c r="E39">
-        <v>-24.82514187149658</v>
+        <v>-25.4197939073398</v>
       </c>
       <c r="F39">
-        <v>-1.097021181020741</v>
+        <v>-0.9680559735484968</v>
       </c>
       <c r="G39">
-        <v>-4.262265632114741</v>
+        <v>-4.270227494136688</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.03843718142685548</v>
       </c>
       <c r="E40">
-        <v>-23.62889112068236</v>
+        <v>-23.97276985140283</v>
       </c>
       <c r="F40">
-        <v>-1.121885456983171</v>
+        <v>-1.323341924241802</v>
       </c>
       <c r="G40">
-        <v>-4.260481248069074</v>
+        <v>-4.505964820897111</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.1851519676021533</v>
       </c>
       <c r="E41">
-        <v>-22.96092761912896</v>
+        <v>-23.35458333614174</v>
       </c>
       <c r="F41">
-        <v>-1.473481859264407</v>
+        <v>-1.380259876855559</v>
       </c>
       <c r="G41">
-        <v>-4.376274199396162</v>
+        <v>-4.155791866480701</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.3349126045328925</v>
       </c>
       <c r="E42">
-        <v>-23.20738076004841</v>
+        <v>-22.72489449690116</v>
       </c>
       <c r="F42">
-        <v>-1.334728662560684</v>
+        <v>-1.335943049173188</v>
       </c>
       <c r="G42">
-        <v>-3.578469140432738</v>
+        <v>-3.981130794374292</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.4800758099972601</v>
       </c>
       <c r="E43">
-        <v>-23.48469092285611</v>
+        <v>-22.61146527995704</v>
       </c>
       <c r="F43">
-        <v>-1.743902397908305</v>
+        <v>-1.364356879456614</v>
       </c>
       <c r="G43">
-        <v>-4.195988510418532</v>
+        <v>-4.031977463311959</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.612375523415576</v>
       </c>
       <c r="E44">
-        <v>-22.44201883953803</v>
+        <v>-23.22837023707396</v>
       </c>
       <c r="F44">
-        <v>-1.506025929418191</v>
+        <v>-1.628934942808568</v>
       </c>
       <c r="G44">
-        <v>-3.873084519609099</v>
+        <v>-4.052340628924016</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.7241383065057134</v>
       </c>
       <c r="E45">
-        <v>-20.56851668698068</v>
+        <v>-21.36190533312453</v>
       </c>
       <c r="F45">
-        <v>-1.270732310490005</v>
+        <v>-1.518016547573714</v>
       </c>
       <c r="G45">
-        <v>-3.513933365690185</v>
+        <v>-4.482840660305301</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.8083477707878166</v>
       </c>
       <c r="E46">
-        <v>-20.97167314246155</v>
+        <v>-20.61388293958952</v>
       </c>
       <c r="F46">
-        <v>-1.403587531285796</v>
+        <v>-1.574473927911514</v>
       </c>
       <c r="G46">
-        <v>-4.22165848053004</v>
+        <v>-3.417536900677687</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.8585342620326102</v>
       </c>
       <c r="E47">
-        <v>-19.02899402096303</v>
+        <v>-20.69537282935755</v>
       </c>
       <c r="F47">
-        <v>-1.178346979157985</v>
+        <v>-1.911526683701799</v>
       </c>
       <c r="G47">
-        <v>-3.818324785844014</v>
+        <v>-4.08834281166359</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.8695820028237853</v>
       </c>
       <c r="E48">
-        <v>-20.56328629950182</v>
+        <v>-20.87514419051405</v>
       </c>
       <c r="F48">
-        <v>-1.165739227287376</v>
+        <v>-1.765456517729149</v>
       </c>
       <c r="G48">
-        <v>-4.976502590030343</v>
+        <v>-4.358589265125375</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.8378525218087362</v>
       </c>
       <c r="E49">
-        <v>-19.15966313845436</v>
+        <v>-19.20171907656359</v>
       </c>
       <c r="F49">
-        <v>-1.356204915845664</v>
+        <v>-1.819575416888846</v>
       </c>
       <c r="G49">
-        <v>-3.090097462479453</v>
+        <v>-4.036069297598498</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.7615935561399723</v>
       </c>
       <c r="E50">
-        <v>-17.97386863412385</v>
+        <v>-18.07153423304728</v>
       </c>
       <c r="F50">
-        <v>-1.420982418377182</v>
+        <v>-1.919013468288301</v>
       </c>
       <c r="G50">
-        <v>-5.376098678802532</v>
+        <v>-4.367726370813764</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.6399349487926494</v>
       </c>
       <c r="E51">
-        <v>-17.42376319709408</v>
+        <v>-18.3920686802582</v>
       </c>
       <c r="F51">
-        <v>-1.463654108397593</v>
+        <v>-1.677094566872525</v>
       </c>
       <c r="G51">
-        <v>-4.560416673927043</v>
+        <v>-4.425048466826245</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.4748563563446433</v>
       </c>
       <c r="E52">
-        <v>-15.89458356570994</v>
+        <v>-17.52535951145616</v>
       </c>
       <c r="F52">
-        <v>-1.299187559143571</v>
+        <v>-2.021248088039608</v>
       </c>
       <c r="G52">
-        <v>-4.736838956260344</v>
+        <v>-4.713598926574661</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.2692531013864832</v>
       </c>
       <c r="E53">
-        <v>-16.02634857391113</v>
+        <v>-16.99022520949575</v>
       </c>
       <c r="F53">
-        <v>-1.606799309070959</v>
+        <v>-1.779424448875154</v>
       </c>
       <c r="G53">
-        <v>-5.856664090374216</v>
+        <v>-4.793406247889871</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.02440135933335585</v>
       </c>
       <c r="E54">
-        <v>-16.45741401470127</v>
+        <v>-16.60340748823455</v>
       </c>
       <c r="F54">
-        <v>-1.446234370284123</v>
+        <v>-1.819659910363931</v>
       </c>
       <c r="G54">
-        <v>-4.795415749032209</v>
+        <v>-4.928496369165371</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.2545851786476353</v>
       </c>
       <c r="E55">
-        <v>-16.06844979676044</v>
+        <v>-15.96052720420964</v>
       </c>
       <c r="F55">
-        <v>-1.62056180510107</v>
+        <v>-2.232393968808785</v>
       </c>
       <c r="G55">
-        <v>-4.786387891346616</v>
+        <v>-5.385593323409162</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.5630160682219083</v>
       </c>
       <c r="E56">
-        <v>-14.71922266549311</v>
+        <v>-15.35479852094365</v>
       </c>
       <c r="F56">
-        <v>-1.436670040251399</v>
+        <v>-1.973814942187905</v>
       </c>
       <c r="G56">
-        <v>-5.551829057118125</v>
+        <v>-5.286270336139948</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.8977043889565516</v>
       </c>
       <c r="E57">
-        <v>-14.82718148583597</v>
+        <v>-15.1506141564118</v>
       </c>
       <c r="F57">
-        <v>-1.602090868753447</v>
+        <v>-2.210434777327973</v>
       </c>
       <c r="G57">
-        <v>-5.786725505311573</v>
+        <v>-5.683237851753955</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.251290010621037</v>
       </c>
       <c r="E58">
-        <v>-14.20765454226861</v>
+        <v>-15.31740691106232</v>
       </c>
       <c r="F58">
-        <v>-1.530659919242643</v>
+        <v>-2.114007841437694</v>
       </c>
       <c r="G58">
-        <v>-5.810683923379279</v>
+        <v>-5.425783346255914</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.616817167472386</v>
       </c>
       <c r="E59">
-        <v>-13.28727389952767</v>
+        <v>-13.79236177644719</v>
       </c>
       <c r="F59">
-        <v>-1.664582077253239</v>
+        <v>-2.440696064284151</v>
       </c>
       <c r="G59">
-        <v>-6.192561972425288</v>
+        <v>-6.040786701631862</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.988627769405051</v>
       </c>
       <c r="E60">
-        <v>-13.92882281219432</v>
+        <v>-14.05052555115047</v>
       </c>
       <c r="F60">
-        <v>-2.003033945586852</v>
+        <v>-2.164346071771014</v>
       </c>
       <c r="G60">
-        <v>-6.803589362608571</v>
+        <v>-5.845305608628976</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.355575331714004</v>
       </c>
       <c r="E61">
-        <v>-12.81491783273559</v>
+        <v>-12.94378008909785</v>
       </c>
       <c r="F61">
-        <v>-1.503675022729046</v>
+        <v>-2.262787597184902</v>
       </c>
       <c r="G61">
-        <v>-6.985076779616957</v>
+        <v>-5.805877011256257</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.707793855486713</v>
       </c>
       <c r="E62">
-        <v>-12.81151242028182</v>
+        <v>-13.05496318293418</v>
       </c>
       <c r="F62">
-        <v>-1.922205996258691</v>
+        <v>-2.309818984846246</v>
       </c>
       <c r="G62">
-        <v>-7.083644962503217</v>
+        <v>-6.71588307963666</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.037647033381654</v>
       </c>
       <c r="E63">
-        <v>-13.22690481253141</v>
+        <v>-13.30690936282492</v>
       </c>
       <c r="F63">
-        <v>-2.261535105671869</v>
+        <v>-2.491754974257907</v>
       </c>
       <c r="G63">
-        <v>-6.955940668325831</v>
+        <v>-6.85169821038526</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.33436222613568</v>
       </c>
       <c r="E64">
-        <v>-12.53922886362262</v>
+        <v>-11.81155290380408</v>
       </c>
       <c r="F64">
-        <v>-1.861219931329785</v>
+        <v>-2.598268111644674</v>
       </c>
       <c r="G64">
-        <v>-6.793124728158936</v>
+        <v>-6.921580516173736</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.591577780770482</v>
       </c>
       <c r="E65">
-        <v>-11.73169326467881</v>
+        <v>-12.78581333028829</v>
       </c>
       <c r="F65">
-        <v>-1.808537421246542</v>
+        <v>-2.40648697565074</v>
       </c>
       <c r="G65">
-        <v>-7.470992032780104</v>
+        <v>-6.391770739705393</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.806667006204217</v>
       </c>
       <c r="E66">
-        <v>-12.01522102229906</v>
+        <v>-13.11604324034963</v>
       </c>
       <c r="F66">
-        <v>-2.257164639254698</v>
+        <v>-2.663411752568229</v>
       </c>
       <c r="G66">
-        <v>-6.445947817455566</v>
+        <v>-6.88427066794615</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.975514632770723</v>
       </c>
       <c r="E67">
-        <v>-11.9321235242583</v>
+        <v>-11.56980937585261</v>
       </c>
       <c r="F67">
-        <v>-2.046218395029596</v>
+        <v>-2.450661324139829</v>
       </c>
       <c r="G67">
-        <v>-7.095089518432478</v>
+        <v>-6.181941742335306</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.098846761733891</v>
       </c>
       <c r="E68">
-        <v>-11.96284016345233</v>
+        <v>-11.93732674089312</v>
       </c>
       <c r="F68">
-        <v>-2.456225467984434</v>
+        <v>-2.770054943637235</v>
       </c>
       <c r="G68">
-        <v>-8.278778386544431</v>
+        <v>-6.435718231739218</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.178528828985709</v>
       </c>
       <c r="E69">
-        <v>-11.47046371307234</v>
+        <v>-12.47080362136672</v>
       </c>
       <c r="F69">
-        <v>-2.210553233866573</v>
+        <v>-2.797753892852045</v>
       </c>
       <c r="G69">
-        <v>-6.361962587669795</v>
+        <v>-7.289968092147216</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.215087830050324</v>
       </c>
       <c r="E70">
-        <v>-11.30712618408968</v>
+        <v>-13.09260385888593</v>
       </c>
       <c r="F70">
-        <v>-2.016800583453978</v>
+        <v>-2.665106592274357</v>
       </c>
       <c r="G70">
-        <v>-8.215421166013858</v>
+        <v>-6.898658298859822</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.211884002645567</v>
       </c>
       <c r="E71">
-        <v>-10.42003435377912</v>
+        <v>-12.0558097348298</v>
       </c>
       <c r="F71">
-        <v>-2.394722501796182</v>
+        <v>-2.806354003227909</v>
       </c>
       <c r="G71">
-        <v>-8.025415715332928</v>
+        <v>-7.174896839747689</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.170994365724407</v>
       </c>
       <c r="E72">
-        <v>-11.62437295917103</v>
+        <v>-11.58634736292863</v>
       </c>
       <c r="F72">
-        <v>-2.146479015260032</v>
+        <v>-2.898041849206773</v>
       </c>
       <c r="G72">
-        <v>-7.359112146280434</v>
+        <v>-6.44902000371601</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.09478897289724</v>
       </c>
       <c r="E73">
-        <v>-12.13006312313357</v>
+        <v>-12.13957291854968</v>
       </c>
       <c r="F73">
-        <v>-2.8339585185588</v>
+        <v>-2.904163484313461</v>
       </c>
       <c r="G73">
-        <v>-7.541645695679229</v>
+        <v>-6.944042567657691</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.98769115902599</v>
       </c>
       <c r="E74">
-        <v>-13.19689461528258</v>
+        <v>-12.56073005821104</v>
       </c>
       <c r="F74">
-        <v>-2.290870080507208</v>
+        <v>-2.957577442813376</v>
       </c>
       <c r="G74">
-        <v>-7.151199954777585</v>
+        <v>-6.106984370235129</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.852090986367665</v>
       </c>
       <c r="E75">
-        <v>-12.54219048562364</v>
+        <v>-12.55561741105638</v>
       </c>
       <c r="F75">
-        <v>-2.561499367736612</v>
+        <v>-3.167085641227219</v>
       </c>
       <c r="G75">
-        <v>-6.142615771874304</v>
+        <v>-6.511463513677743</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.691992141054692</v>
       </c>
       <c r="E76">
-        <v>-13.16960150243835</v>
+        <v>-12.32587433922524</v>
       </c>
       <c r="F76">
-        <v>-2.368405269409241</v>
+        <v>-2.992990149283055</v>
       </c>
       <c r="G76">
-        <v>-7.023995552976629</v>
+        <v>-5.646497417359124</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.513473661264599</v>
       </c>
       <c r="E77">
-        <v>-12.87046862338768</v>
+        <v>-13.22260276222413</v>
       </c>
       <c r="F77">
-        <v>-2.913147128796822</v>
+        <v>-3.513003584962264</v>
       </c>
       <c r="G77">
-        <v>-6.995362644607472</v>
+        <v>-6.005728024370979</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.32015973571818</v>
       </c>
       <c r="E78">
-        <v>-14.21582843785246</v>
+        <v>-13.58389347550408</v>
       </c>
       <c r="F78">
-        <v>-2.612811758135624</v>
+        <v>-3.14057374250062</v>
       </c>
       <c r="G78">
-        <v>-5.694493706587478</v>
+        <v>-5.168789006587831</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.117906634664069</v>
       </c>
       <c r="E79">
-        <v>-15.07593509155131</v>
+        <v>-14.23373402407879</v>
       </c>
       <c r="F79">
-        <v>-2.765608267419007</v>
+        <v>-3.214991784865919</v>
       </c>
       <c r="G79">
-        <v>-5.491643339214175</v>
+        <v>-5.040988706589806</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.912757744900971</v>
       </c>
       <c r="E80">
-        <v>-14.50197818192314</v>
+        <v>-14.53606400577887</v>
       </c>
       <c r="F80">
-        <v>-2.95887466616616</v>
+        <v>-3.622747355219948</v>
       </c>
       <c r="G80">
-        <v>-5.760744343919373</v>
+        <v>-5.666572565509265</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.707032315926463</v>
       </c>
       <c r="E81">
-        <v>-15.12021903887232</v>
+        <v>-16.16535461205058</v>
       </c>
       <c r="F81">
-        <v>-2.924733503659778</v>
+        <v>-3.284611094866801</v>
       </c>
       <c r="G81">
-        <v>-5.624776928075966</v>
+        <v>-5.064960366839669</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.505555705815925</v>
       </c>
       <c r="E82">
-        <v>-16.13794828735616</v>
+        <v>-16.29534445844076</v>
       </c>
       <c r="F82">
-        <v>-3.265074049671775</v>
+        <v>-3.206936740241097</v>
       </c>
       <c r="G82">
-        <v>-5.450840865442657</v>
+        <v>-5.164078100285448</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.313860988896134</v>
       </c>
       <c r="E83">
-        <v>-16.78644840762459</v>
+        <v>-17.24121135289687</v>
       </c>
       <c r="F83">
-        <v>-2.681692164413209</v>
+        <v>-3.553396436257573</v>
       </c>
       <c r="G83">
-        <v>-5.991651584737999</v>
+        <v>-4.447513828855739</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.1360573848365</v>
       </c>
       <c r="E84">
-        <v>-19.71279812459526</v>
+        <v>-17.8799118554127</v>
       </c>
       <c r="F84">
-        <v>-3.542824811463046</v>
+        <v>-3.786326722985572</v>
       </c>
       <c r="G84">
-        <v>-5.17928674649286</v>
+        <v>-4.053270892220551</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.979327260251296</v>
       </c>
       <c r="E85">
-        <v>-18.12025155642179</v>
+        <v>-19.27550150357056</v>
       </c>
       <c r="F85">
-        <v>-3.095216485360333</v>
+        <v>-3.61553973044819</v>
       </c>
       <c r="G85">
-        <v>-5.536160245080755</v>
+        <v>-4.733505236902298</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.853496092592116</v>
       </c>
       <c r="E86">
-        <v>-19.80438651140039</v>
+        <v>-20.90077535339746</v>
       </c>
       <c r="F86">
-        <v>-2.558820427555958</v>
+        <v>-3.93106156070491</v>
       </c>
       <c r="G86">
-        <v>-4.259021297486255</v>
+        <v>-4.48670737749517</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.766488874939696</v>
       </c>
       <c r="E87">
-        <v>-20.4635557164309</v>
+        <v>-21.02019121297973</v>
       </c>
       <c r="F87">
-        <v>-3.513170915177629</v>
+        <v>-3.53303185202715</v>
       </c>
       <c r="G87">
-        <v>-4.823191226106694</v>
+        <v>-3.888081290901997</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.725587135404122</v>
       </c>
       <c r="E88">
-        <v>-22.0121398589379</v>
+        <v>-23.36884350079189</v>
       </c>
       <c r="F88">
-        <v>-3.226637802181878</v>
+        <v>-3.717378390580958</v>
       </c>
       <c r="G88">
-        <v>-4.159284492024632</v>
+        <v>-3.779270280117232</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.739786768551049</v>
       </c>
       <c r="E89">
-        <v>-23.61107157546218</v>
+        <v>-23.31807930716591</v>
       </c>
       <c r="F89">
-        <v>-2.924233169748487</v>
+        <v>-3.687051031597065</v>
       </c>
       <c r="G89">
-        <v>-4.875458119080707</v>
+        <v>-3.952868667105534</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.814723330736746</v>
       </c>
       <c r="E90">
-        <v>-24.14881880692502</v>
+        <v>-25.93631618112869</v>
       </c>
       <c r="F90">
-        <v>-3.416842555008283</v>
+        <v>-3.779539080487033</v>
       </c>
       <c r="G90">
-        <v>-3.881135766360607</v>
+        <v>-2.927192137582996</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.952512338162639</v>
       </c>
       <c r="E91">
-        <v>-25.78227560928378</v>
+        <v>-27.17111783117021</v>
       </c>
       <c r="F91">
-        <v>-2.969804974046099</v>
+        <v>-4.119833237924473</v>
       </c>
       <c r="G91">
-        <v>-4.404711785578502</v>
+        <v>-4.710410871220343</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.157437845672924</v>
       </c>
       <c r="E92">
-        <v>-28.2550035564321</v>
+        <v>-28.34590814366208</v>
       </c>
       <c r="F92">
-        <v>-2.945678773439564</v>
+        <v>-4.10967745356615</v>
       </c>
       <c r="G92">
-        <v>-3.933048430961918</v>
+        <v>-4.142427194138663</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.427149347116857</v>
       </c>
       <c r="E93">
-        <v>-29.2551804396622</v>
+        <v>-30.82324607735021</v>
       </c>
       <c r="F93">
-        <v>-3.29864529540503</v>
+        <v>-4.058123179885521</v>
       </c>
       <c r="G93">
-        <v>-4.501104940045461</v>
+        <v>-4.415328705122945</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.752936421523194</v>
       </c>
       <c r="E94">
-        <v>-31.92904282409821</v>
+        <v>-32.7742326844158</v>
       </c>
       <c r="F94">
-        <v>-3.761478186003795</v>
+        <v>-4.201892141213194</v>
       </c>
       <c r="G94">
-        <v>-4.729052553151979</v>
+        <v>-4.387566470230616</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.129057666664401</v>
       </c>
       <c r="E95">
-        <v>-33.67745946761569</v>
+        <v>-35.51093217418224</v>
       </c>
       <c r="F95">
-        <v>-3.437862377854321</v>
+        <v>-4.345468921303419</v>
       </c>
       <c r="G95">
-        <v>-5.201003925230479</v>
+        <v>-4.459428482251576</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.547102177722205</v>
       </c>
       <c r="E96">
-        <v>-35.87156399449407</v>
+        <v>-36.20170559931227</v>
       </c>
       <c r="F96">
-        <v>-3.735812050395455</v>
+        <v>-4.052574775021569</v>
       </c>
       <c r="G96">
-        <v>-4.897926791655741</v>
+        <v>-5.167335677096091</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.985958869171976</v>
       </c>
       <c r="E97">
-        <v>-38.1280301369321</v>
+        <v>-38.6105594205824</v>
       </c>
       <c r="F97">
-        <v>-3.949304696016763</v>
+        <v>-4.236594108451271</v>
       </c>
       <c r="G97">
-        <v>-5.059984616894144</v>
+        <v>-5.126129316768782</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.443196878971142</v>
       </c>
       <c r="E98">
-        <v>-40.22140102374686</v>
+        <v>-41.28515088933364</v>
       </c>
       <c r="F98">
-        <v>-4.216556729344954</v>
+        <v>-4.268828369196409</v>
       </c>
       <c r="G98">
-        <v>-6.034907172754116</v>
+        <v>-5.96929878125684</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.892130606391277</v>
       </c>
       <c r="E99">
-        <v>-41.7106168720133</v>
+        <v>-42.97011681929265</v>
       </c>
       <c r="F99">
-        <v>-4.347826454931786</v>
+        <v>-4.497924143216848</v>
       </c>
       <c r="G99">
-        <v>-7.421499376967999</v>
+        <v>-6.368712790024369</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.335079154580474</v>
       </c>
       <c r="E100">
-        <v>-43.71804411487349</v>
+        <v>-44.52217656560054</v>
       </c>
       <c r="F100">
-        <v>-3.888091658419491</v>
+        <v>-4.748927749939126</v>
       </c>
       <c r="G100">
-        <v>-6.874762781157362</v>
+        <v>-6.491361881163288</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.733322858447574</v>
       </c>
       <c r="E101">
-        <v>-46.37853617980185</v>
+        <v>-46.86073714908661</v>
       </c>
       <c r="F101">
-        <v>-4.440772590995502</v>
+        <v>-4.691106876856318</v>
       </c>
       <c r="G101">
-        <v>-6.492606646286054</v>
+        <v>-6.305785940413903</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.129997033605517</v>
       </c>
       <c r="E102">
-        <v>-49.13701310107118</v>
+        <v>-49.13928299866753</v>
       </c>
       <c r="F102">
-        <v>-4.344533694505658</v>
+        <v>-4.691313968707018</v>
       </c>
       <c r="G102">
-        <v>-6.107812006619946</v>
+        <v>-6.829279195993315</v>
       </c>
     </row>
   </sheetData>
